--- a/results/Int Task Remove ACC -1.0/Linea_fi_all.xlsx
+++ b/results/Int Task Remove ACC -1.0/Linea_fi_all.xlsx
@@ -1366,7 +1366,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0.019197876732527243 +/- 0.0035741133826272245</t>
+          <t>0.01916838690651721 +/- 0.0035996920128970066</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -1446,7 +1446,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-0.00448245355352408 +/- 0.004385564481278981</t>
+          <t>-0.0045119433795341 +/- 0.0043801078843288994</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.001834862385321101 +/- 0.0027020330773633383</t>
+          <t>0.0018644569399230537 +/- 0.0027254319313034315</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
+          <t>-0.0037289138798461074 +/- 0.005966367901655453</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
           <t>-0.0037585084344480602 +/- 0.005923422370632303</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>-0.0037289138798461074 +/- 0.005966367901655453</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.014150664697193472 +/- 0.0032184620449664664</t>
+          <t>0.01412112259970454 +/- 0.003216698987017147</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -2241,7 +2241,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.0013589364844903916 +/- 0.000701585943104157</t>
+          <t>0.0013884785819793133 +/- 0.0007120809922123419</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>0.0016248153618906858 +/- 0.002472551788322106</t>
+          <t>0.0016543574593796072 +/- 0.002454662106687253</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.04212551805802254 +/- 0.0029987150449135446</t>
+          <t>0.042155121373593875 +/- 0.0030079066420084038</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -2706,7 +2706,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0.02735346358792188 +/- 0.003373219546061369</t>
+          <t>0.027323860272350543 +/- 0.0034012908463510756</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>0.003049141503848474 +/- 0.0006492513972605428</t>
+          <t>0.0030195381882771265 +/- 0.0006724580634458557</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
@@ -3351,12 +3351,12 @@
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>0.06903791914760264 +/- 0.005266392592344207</t>
+          <t>0.06906925728611722 +/- 0.005298277456698978</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>0.025227201504230655 +/- 0.003087244074015737</t>
+          <t>0.025195863365716088 +/- 0.003022790486189269</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
@@ -3561,7 +3561,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.07815912636505461 +/- 0.00518025292420096</t>
+          <t>0.07822152886115447 +/- 0.0052005096116385695</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -3586,7 +3586,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.1069266770670827 +/- 0.006059873591642024</t>
+          <t>0.10695787831513259 +/- 0.006093117253658224</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>0.09422776911076444 +/- 0.004291731385722156</t>
+          <t>0.09419656786271453 +/- 0.004251735352930298</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.014353079870321283 +/- 0.005145537478623378</t>
+          <t>0.014382552313586826 +/- 0.005131591647182295</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4051,7 +4051,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.016681402888299467 +/- 0.002982984009167109</t>
+          <t>0.016651930445033925 +/- 0.003017868818015208</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -4071,7 +4071,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>0.006130268199233735 +/- 0.0024651368896347376</t>
+          <t>0.006100795755968192 +/- 0.0024905522473708396</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>-0.0014441497200117447 +/- 0.0007847643357320394</t>
+          <t>-0.0014441497200117447 +/- 0.0007847643357320395</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
@@ -4141,7 +4141,7 @@
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>-0.15284409077512523 +/- 0.004323919819650645</t>
+          <t>-0.15287356321839077 +/- 0.004262921742749576</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
@@ -4251,7 +4251,7 @@
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-0.00023577954612433727 +/- 0.0028780561428196345</t>
+          <t>-0.00020630710285879372 +/- 0.002887848295964399</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-0.021898025346301152 +/- 0.0017187766945857001</t>
+          <t>-0.021868552903035597 +/- 0.0017426166223512413</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>-0.02452107279693483 +/- 0.0029789045136441464</t>
+          <t>-0.024491600353669284 +/- 0.002995334157730999</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>0.005214635551714275 +/- 0.0006872290660833595</t>
+          <t>0.005214635551714275 +/- 0.0007884720359207123</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4801,72 +4801,72 @@
       </c>
       <c r="BW10" t="inlineStr">
         <is>
+          <t>0.04281186977816197 +/- 0.0027368117745982094</t>
+        </is>
+      </c>
+      <c r="BX10" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="BY10" t="inlineStr">
+        <is>
+          <t>-0.0004321521175453147 +/- 0.0006344775438071024</t>
+        </is>
+      </c>
+      <c r="BZ10" t="inlineStr">
+        <is>
+          <t>-0.0004321521175453147 +/- 0.0006344775438071024</t>
+        </is>
+      </c>
+      <c r="CA10" t="inlineStr">
+        <is>
+          <t>0.0018438490348603232 +/- 0.0008270066317722478</t>
+        </is>
+      </c>
+      <c r="CB10" t="inlineStr">
+        <is>
+          <t>0.0015845577643330943 +/- 0.00023227478387491588</t>
+        </is>
+      </c>
+      <c r="CC10" t="inlineStr">
+        <is>
+          <t>0.004984154422356735 +/- 0.0006448582335234801</t>
+        </is>
+      </c>
+      <c r="CD10" t="inlineStr">
+        <is>
+          <t>-0.004753673292999083 +/- 0.0005797929068711492</t>
+        </is>
+      </c>
+      <c r="CE10" t="inlineStr">
+        <is>
+          <t>0.0020167098818784867 +/- 0.001249177953827647</t>
+        </is>
+      </c>
+      <c r="CF10" t="inlineStr">
+        <is>
+          <t>-0.0003745318352059268 +/- 0.001804030216589248</t>
+        </is>
+      </c>
+      <c r="CG10" t="inlineStr">
+        <is>
+          <t>0.009651397291846785 +/- 0.0023414333360159928</t>
+        </is>
+      </c>
+      <c r="CH10" t="inlineStr">
+        <is>
+          <t>-0.0002016709881878076 +/- 0.00025929127052721644</t>
+        </is>
+      </c>
+      <c r="CI10" t="inlineStr">
+        <is>
+          <t>0.0625756266205705 +/- 0.0036437710754854296</t>
+        </is>
+      </c>
+      <c r="CJ10" t="inlineStr">
+        <is>
           <t>0.042783059636992284 +/- 0.002770121666162239</t>
-        </is>
-      </c>
-      <c r="BX10" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="BY10" t="inlineStr">
-        <is>
-          <t>-0.0004321521175453147 +/- 0.0006344775438071024</t>
-        </is>
-      </c>
-      <c r="BZ10" t="inlineStr">
-        <is>
-          <t>-0.0004321521175453147 +/- 0.0006344775438071024</t>
-        </is>
-      </c>
-      <c r="CA10" t="inlineStr">
-        <is>
-          <t>0.0018438490348603232 +/- 0.0008270066317722478</t>
-        </is>
-      </c>
-      <c r="CB10" t="inlineStr">
-        <is>
-          <t>0.0015845577643330943 +/- 0.00023227478387491588</t>
-        </is>
-      </c>
-      <c r="CC10" t="inlineStr">
-        <is>
-          <t>0.004984154422356735 +/- 0.0006448582335234801</t>
-        </is>
-      </c>
-      <c r="CD10" t="inlineStr">
-        <is>
-          <t>-0.004753673292999083 +/- 0.0005797929068711492</t>
-        </is>
-      </c>
-      <c r="CE10" t="inlineStr">
-        <is>
-          <t>0.0020167098818784867 +/- 0.001249177953827647</t>
-        </is>
-      </c>
-      <c r="CF10" t="inlineStr">
-        <is>
-          <t>-0.0003745318352059268 +/- 0.001804030216589248</t>
-        </is>
-      </c>
-      <c r="CG10" t="inlineStr">
-        <is>
-          <t>0.009651397291846785 +/- 0.0023414333360159928</t>
-        </is>
-      </c>
-      <c r="CH10" t="inlineStr">
-        <is>
-          <t>-0.0002016709881878076 +/- 0.00025929127052721644</t>
-        </is>
-      </c>
-      <c r="CI10" t="inlineStr">
-        <is>
-          <t>0.0625756266205705 +/- 0.0036437710754854296</t>
-        </is>
-      </c>
-      <c r="CJ10" t="inlineStr">
-        <is>
-          <t>0.04281186977816197 +/- 0.0027368117745982094</t>
         </is>
       </c>
       <c r="CK10" t="inlineStr">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.09289113622843544 +/- 0.0032854889014400997</t>
+          <t>0.09289113622843544 +/- 0.0033442058831916195</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -4916,74 +4916,74 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
+          <t>0.000832837596668623 +/- 0.0016171656417689705</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>0.11290898274836406 +/- 0.005504204170922269</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0.034741225461035065 +/- 0.004114602371395736</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>0.034741225461035065 +/- 0.004114602371395736</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>0.03512790005948838 +/- 0.002532452689617296</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>0.1414039262343843 +/- 0.004017559549054867</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>0.025669244497322996 +/- 0.002517034265085082</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>0.02013682331945269 +/- 0.0029775414911601583</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>0.012284354550862565 +/- 0.0027553149071078693</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>0.050029744199881 +/- 0.0031668843912447766</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>0.42560975609756097 +/- 0.005276473509503083</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>0.0035990481856037703 +/- 0.00256024831088703</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>0.06177870315288515 +/- 0.005382056601623119</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
           <t>0.000862581796549644 +/- 0.0016261673923660509</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>0.11290898274836406 +/- 0.005504204170922269</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>0.034741225461035065 +/- 0.004114602371395736</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>0.034741225461035065 +/- 0.004114602371395736</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>0.03512790005948838 +/- 0.002532452689617296</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>0.14137418203450328 +/- 0.004028225703778093</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>0.025639500297441976 +/- 0.0024914207723226683</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>0.02013682331945269 +/- 0.0029775414911601583</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>0.012284354550862565 +/- 0.0027553149071078693</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>0.050029744199881 +/- 0.0031668843912447766</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>0.42560975609756097 +/- 0.005276473509503083</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>0.0035990481856037703 +/- 0.00256024831088703</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>0.06177870315288515 +/- 0.005382056601623119</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>0.000832837596668623 +/- 0.0016171656417689705</t>
-        </is>
-      </c>
       <c r="W11" t="inlineStr">
         <is>
           <t>0.019541939321832236 +/- 0.0029235688905886867</t>
@@ -5276,7 +5276,7 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>0.003063652587745358 +/- 0.0007045044189367789</t>
+          <t>0.003093396787626379 +/- 0.0007063856089850196</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
